--- a/CleanedOxygenThresholds.xlsx
+++ b/CleanedOxygenThresholds.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/isabellashowman/Library/CloudStorage/OneDrive-Personal/EarthLab Internship/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69775498-38FB-D74E-9EDD-EFC19E590B98}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5ED689B1-DED9-2140-B07F-EA54BE4B74AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7080" yWindow="1640" windowWidth="25120" windowHeight="19020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="11540" yWindow="10700" windowWidth="25120" windowHeight="19020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1194,9 +1194,6 @@
   </si>
   <si>
     <t>Used formula to estimate the ambient oxygen level required to maintain respiration at a rate independent of the environmental supply. Values from Table V.</t>
-  </si>
-  <si>
-    <t>**They designed a two-factor trial including temperature at 13 °C, 17 °C, and 21 °C and DO content at 4.2 and 9.6 mg L−1 with three replicates for each treatment. The water temperature was gradually altered from 16 °C to 13 °C, 17 °C, and 21 °C at a rate of 1 °C per 2 h using a temperature control system</t>
   </si>
   <si>
     <t>Pcrit; defined as the oxygen tension at which an animal converts from regulating internal oxygen levels to conforming to the environmental oxygen tension. From the swim-up stage through early development (total of 30 weeks), each group was fed their prescribed, steam-pelleted, dry diet that contained one of four concentrations of refined canola oil (CO). Feeding was conducted by hand 3–6 times daily. No significant differences were observed among treatments. (n = 10), so the %CO.</t>
@@ -1603,29 +1600,6 @@
     <t>Vargo S. L. and Sastry A. N. 1977. Acute temperature and low dissolved oxygen tolerances of brachyuran crab (Cancer irroratus) larvae. Marine Biology. 40:165–171.</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>***Should we just use the V50 value of retinal function?</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> Retinal function at 90%. The PO2 of this solution was adjusted by changing the gas concentrations and flow rate of aeration</t>
-    </r>
-  </si>
-  <si>
     <t>Klyashtorin, L.B. 1975. The sensitivity of young Salmonidae to oxygen deficiency. Journal of Ichthyology. 15:337-341</t>
   </si>
   <si>
@@ -1714,6 +1688,13 @@
   </si>
   <si>
     <t xml:space="preserve">GR. Critical DO concentrations were defined as the point at which a fish lost its equilibrium for a period of 10 s. differences in critical DO concentrations when decreases in DO were prolonged. Formalin interaction is included in all of these experiments, </t>
+  </si>
+  <si>
+    <t>They designed a two-factor trial including temperature at 13 °C, 17 °C, and 21 °C and DO content at 4.2 and 9.6 mg L−1 with three replicates for each treatment. The water temperature was gradually altered from 16 °C to 13 °C, 17 °C, and 21 °C at a rate of 1 °C per 2 h using a temperature control system. "At the end of the trial, the survival of rainbow trout was
+significantly higher under high DO conditions (H13, H17, and H21) than under low DO conditions (L13, L17, and L21), indicating that a DO content of about 4 mg L− 1 is the threshold for survival in this species."</t>
+  </si>
+  <si>
+    <t>Retinal function at 90%. The PO2 of this solution was adjusted by changing the gas concentrations and flow rate of aeration</t>
   </si>
 </sst>
 </file>
@@ -2076,7 +2057,7 @@
         <v>193</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="D1" s="5" t="s">
         <v>194</v>
@@ -2085,7 +2066,7 @@
         <v>195</v>
       </c>
       <c r="F1" s="5" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="G1" s="5" t="s">
         <v>331</v>
@@ -2109,13 +2090,13 @@
         <v>199</v>
       </c>
       <c r="N1" s="5" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="O1" s="5" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="P1" s="5" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
       <c r="Q1" s="5" t="s">
         <v>218</v>
@@ -2202,7 +2183,7 @@
         <v>217</v>
       </c>
       <c r="AS1" s="5" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
     </row>
     <row r="2" spans="1:45" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -2213,7 +2194,7 @@
         <v>1</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="D2" t="s">
         <v>2</v>
@@ -2234,7 +2215,7 @@
         <v>335</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="K2">
         <v>10</v>
@@ -2249,7 +2230,7 @@
         <v>4.0599999999999997E-2</v>
       </c>
       <c r="Q2" s="6" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="X2">
         <v>1</v>
@@ -2302,12 +2283,12 @@
         <v>3</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="H3" s="1"/>
       <c r="I3" s="1"/>
       <c r="J3" s="1" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="K3">
         <v>10</v>
@@ -2322,7 +2303,7 @@
         <v>3.4299999999999997E-2</v>
       </c>
       <c r="Q3" s="6" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="X3">
         <v>1</v>
@@ -2366,12 +2347,12 @@
         <v>3</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="H4" s="1"/>
       <c r="I4" s="1"/>
       <c r="J4" s="1" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="K4">
         <v>5</v>
@@ -2383,7 +2364,7 @@
         <v>5</v>
       </c>
       <c r="Q4" s="6" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="X4">
         <v>1</v>
@@ -2421,12 +2402,12 @@
         <v>3</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="H5" s="1"/>
       <c r="I5" s="1"/>
       <c r="J5" s="1" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="K5">
         <v>10</v>
@@ -2441,7 +2422,7 @@
         <v>2.6800000000000001E-2</v>
       </c>
       <c r="Q5" s="6" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="X5">
         <v>1</v>
@@ -2518,7 +2499,7 @@
         <v>5.5999999999999999E-3</v>
       </c>
       <c r="Q6" s="6" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="T6">
         <v>2</v>
@@ -2584,7 +2565,7 @@
       </c>
       <c r="P7" s="1"/>
       <c r="Q7" s="6" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="U7" s="1" t="s">
         <v>220</v>
@@ -2665,7 +2646,7 @@
       </c>
       <c r="P8" s="1"/>
       <c r="Q8" s="6" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="U8" s="1" t="s">
         <v>220</v>
@@ -2743,7 +2724,7 @@
       </c>
       <c r="P9" s="1"/>
       <c r="Q9" s="6" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="U9" s="1" t="s">
         <v>220</v>
@@ -2805,7 +2786,7 @@
         <v>335</v>
       </c>
       <c r="J10" s="1" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="K10">
         <v>0.5</v>
@@ -2820,7 +2801,7 @@
         <v>6.0000000000000001E-3</v>
       </c>
       <c r="Q10" s="6" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="U10" s="1" t="s">
         <v>220</v>
@@ -2882,7 +2863,7 @@
         <v>0.06</v>
       </c>
       <c r="Q11" s="6" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="U11" s="1" t="s">
         <v>220</v>
@@ -2944,7 +2925,7 @@
         <v>0.41299999999999998</v>
       </c>
       <c r="Q12" s="6" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="U12" s="1" t="s">
         <v>220</v>
@@ -3006,7 +2987,7 @@
         <v>0.28000000000000003</v>
       </c>
       <c r="Q13" s="6" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="U13" s="1" t="s">
         <v>220</v>
@@ -3068,7 +3049,7 @@
         <v>0.78</v>
       </c>
       <c r="Q14" s="6" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="U14" s="1" t="s">
         <v>220</v>
@@ -3130,7 +3111,7 @@
         <v>0.70099999999999996</v>
       </c>
       <c r="Q15" s="6" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="U15" s="1" t="s">
         <v>220</v>
@@ -3192,7 +3173,7 @@
         <v>0.26</v>
       </c>
       <c r="Q16" s="6" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="T16">
         <v>1.44</v>
@@ -3266,7 +3247,7 @@
         <v>0.39</v>
       </c>
       <c r="Q17" s="6" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="T17">
         <v>1.1000000000000001</v>
@@ -3337,7 +3318,7 @@
         <v>5</v>
       </c>
       <c r="Q18" s="6" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="X18">
         <v>1</v>
@@ -3393,7 +3374,7 @@
         <v>5</v>
       </c>
       <c r="Q19" s="6" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="X19">
         <v>1</v>
@@ -3449,7 +3430,7 @@
         <v>5</v>
       </c>
       <c r="Q20" s="6" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="X20">
         <v>1</v>
@@ -3505,7 +3486,7 @@
         <v>5</v>
       </c>
       <c r="Q21" s="6" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="X21">
         <v>1</v>
@@ -3552,7 +3533,7 @@
         <v>335</v>
       </c>
       <c r="J22" s="1" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="K22">
         <v>13</v>
@@ -3568,7 +3549,7 @@
       </c>
       <c r="P22" s="1"/>
       <c r="Q22" s="6" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="U22" s="1" t="s">
         <v>220</v>
@@ -3628,7 +3609,7 @@
       </c>
       <c r="P23" s="1"/>
       <c r="Q23" s="6" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="U23" s="1" t="s">
         <v>220</v>
@@ -3685,7 +3666,7 @@
       </c>
       <c r="P24" s="1"/>
       <c r="Q24" s="6" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="U24" s="1" t="s">
         <v>220</v>
@@ -3745,7 +3726,7 @@
       </c>
       <c r="P25" s="1"/>
       <c r="Q25" s="6" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="R25">
         <v>2</v>
@@ -3786,16 +3767,16 @@
         <v>3</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="I26" s="1" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="J26" s="1" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="K26">
         <v>8</v>
@@ -3810,7 +3791,7 @@
         <v>61</v>
       </c>
       <c r="Q26" s="6" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="R26">
         <v>4</v>
@@ -3891,7 +3872,7 @@
       </c>
       <c r="P27" s="1"/>
       <c r="Q27" s="6" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="T27">
         <v>1.61</v>
@@ -3941,7 +3922,7 @@
         <v>335</v>
       </c>
       <c r="J28" s="1" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="K28">
         <v>10</v>
@@ -3956,7 +3937,7 @@
         <v>70</v>
       </c>
       <c r="Q28" s="6" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="T28">
         <v>0.85</v>
@@ -4021,7 +4002,7 @@
         <v>71</v>
       </c>
       <c r="Q29" s="6" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="T29">
         <v>0.73</v>
@@ -4086,7 +4067,7 @@
         <v>72</v>
       </c>
       <c r="Q30" s="6" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="T30">
         <v>0.39</v>
@@ -4133,7 +4114,7 @@
         <v>342</v>
       </c>
       <c r="J31" s="1" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="K31">
         <v>10</v>
@@ -4145,7 +4126,7 @@
         <v>79</v>
       </c>
       <c r="Q31" s="6" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="U31" s="1" t="s">
         <v>220</v>
@@ -4204,7 +4185,7 @@
         <v>79</v>
       </c>
       <c r="Q32" s="6" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="U32" s="1" t="s">
         <v>220</v>
@@ -4257,7 +4238,7 @@
         <v>340</v>
       </c>
       <c r="J33" s="1" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="K33">
         <v>12.8</v>
@@ -4269,7 +4250,7 @@
         <v>79</v>
       </c>
       <c r="Q33" s="6" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="U33" s="1" t="s">
         <v>220</v>
@@ -4287,7 +4268,7 @@
         <v>12.9</v>
       </c>
       <c r="AR33" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="AS33" s="1" t="s">
         <v>88</v>
@@ -4322,7 +4303,7 @@
         <v>342</v>
       </c>
       <c r="J34" s="1" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="K34">
         <v>6.8</v>
@@ -4334,11 +4315,11 @@
         <v>5</v>
       </c>
       <c r="Q34" s="6" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="U34" s="1"/>
       <c r="AR34" s="1" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="AS34" s="1" t="s">
         <v>92</v>
@@ -4385,10 +4366,10 @@
         <v>95</v>
       </c>
       <c r="Q35" s="6" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="U35" s="1" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="Y35">
         <v>5</v>
@@ -4397,7 +4378,7 @@
         <v>22</v>
       </c>
       <c r="AR35" s="1" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="AS35" s="1" t="s">
         <v>96</v>
@@ -4432,7 +4413,7 @@
         <v>376</v>
       </c>
       <c r="J36" s="1" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="K36">
         <v>10</v>
@@ -4447,7 +4428,7 @@
         <v>33.299999999999997</v>
       </c>
       <c r="Q36" s="6" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="X36">
         <v>1</v>
@@ -4503,22 +4484,22 @@
         <v>101</v>
       </c>
       <c r="G37" s="1" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="H37" s="1" t="s">
         <v>375</v>
       </c>
       <c r="I37" s="1" t="s">
+        <v>444</v>
+      </c>
+      <c r="J37" s="1" t="s">
         <v>445</v>
-      </c>
-      <c r="J37" s="1" t="s">
-        <v>446</v>
       </c>
       <c r="K37">
         <v>15</v>
       </c>
       <c r="Q37" s="6" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="X37">
         <v>1</v>
@@ -4574,7 +4555,7 @@
         <v>345</v>
       </c>
       <c r="J38" s="1" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="K38">
         <v>7</v>
@@ -4586,7 +4567,7 @@
         <v>116</v>
       </c>
       <c r="Q38" s="6" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="R38">
         <v>6.4</v>
@@ -4645,7 +4626,7 @@
         <v>95</v>
       </c>
       <c r="Q39" s="6" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="U39" s="1" t="s">
         <v>220</v>
@@ -4689,13 +4670,13 @@
         <v>373</v>
       </c>
       <c r="H40" s="3" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="I40" s="3" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="J40" s="3" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
       <c r="K40" s="3">
         <v>7.4</v>
@@ -4710,13 +4691,13 @@
         <v>73</v>
       </c>
       <c r="O40" s="1" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="P40" s="1" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="Q40" s="4" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="R40" s="3"/>
       <c r="S40" s="3"/>
@@ -4736,7 +4717,7 @@
         <v>1</v>
       </c>
       <c r="AI40" s="1" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="AJ40" s="3">
         <v>73</v>
@@ -4772,10 +4753,10 @@
         <v>373</v>
       </c>
       <c r="H41" s="3" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="I41" s="3" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="J41" s="3" t="s">
         <v>118</v>
@@ -4793,13 +4774,13 @@
         <v>69</v>
       </c>
       <c r="O41" s="1" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="P41" s="1" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="Q41" s="4" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="R41" s="3"/>
       <c r="S41" s="3"/>
@@ -4819,7 +4800,7 @@
         <v>1</v>
       </c>
       <c r="AI41" s="1" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="AJ41" s="3">
         <v>69</v>
@@ -4852,10 +4833,10 @@
         <v>373</v>
       </c>
       <c r="H42" s="3" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="I42" s="3" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="J42" s="3" t="s">
         <v>121</v>
@@ -4873,13 +4854,13 @@
         <v>66</v>
       </c>
       <c r="O42" s="1" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="P42" s="1" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="Q42" s="4" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="R42" s="3"/>
       <c r="S42" s="3"/>
@@ -4899,7 +4880,7 @@
         <v>1</v>
       </c>
       <c r="AI42" s="1" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="AJ42" s="3">
         <v>66</v>
@@ -4932,13 +4913,13 @@
         <v>373</v>
       </c>
       <c r="H43" s="3" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="I43" s="3" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="J43" s="3" t="s">
-        <v>544</v>
+        <v>542</v>
       </c>
       <c r="K43" s="3">
         <v>16.5</v>
@@ -4953,13 +4934,13 @@
         <v>50.8</v>
       </c>
       <c r="O43" s="1" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="P43" s="1" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="Q43" s="4" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="R43" s="3"/>
       <c r="S43" s="3"/>
@@ -4979,7 +4960,7 @@
         <v>1320</v>
       </c>
       <c r="AI43" s="1" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="AJ43" s="3">
         <v>50.8</v>
@@ -5015,13 +4996,13 @@
         <v>372</v>
       </c>
       <c r="H44" s="3" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="I44" s="3" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="J44" s="3" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="K44" s="3">
         <v>15</v>
@@ -5036,13 +5017,13 @@
         <v>1400</v>
       </c>
       <c r="O44" s="1" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="P44" s="1" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="Q44" s="4" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="R44" s="3"/>
       <c r="S44" s="3"/>
@@ -5053,7 +5034,7 @@
         <v>7</v>
       </c>
       <c r="AI44" s="1" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="AL44" s="3">
         <v>2000</v>
@@ -5062,7 +5043,7 @@
         <v>800</v>
       </c>
       <c r="AR44" s="3" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="AS44" s="3" t="s">
         <v>127</v>
@@ -5091,13 +5072,13 @@
         <v>373</v>
       </c>
       <c r="H45" s="3" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="I45" s="3" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="J45" s="3" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="K45" s="3">
         <v>10</v>
@@ -5112,13 +5093,13 @@
         <v>104.5</v>
       </c>
       <c r="O45" s="1" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="P45" s="1" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="Q45" s="4" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="R45" s="3"/>
       <c r="S45" s="3"/>
@@ -5144,7 +5125,7 @@
         <v>80</v>
       </c>
       <c r="AI45" s="1" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="AJ45" s="3">
         <v>104.5</v>
@@ -5183,10 +5164,10 @@
         <v>373</v>
       </c>
       <c r="H46" s="3" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="I46" s="3" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="J46" s="3" t="s">
         <v>131</v>
@@ -5204,13 +5185,13 @@
         <v>107.5</v>
       </c>
       <c r="O46" s="1" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="P46" s="1" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="Q46" s="4" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="R46" s="3"/>
       <c r="S46" s="3"/>
@@ -5236,7 +5217,7 @@
         <v>80</v>
       </c>
       <c r="AI46" s="1" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="AJ46" s="3">
         <v>107.5</v>
@@ -5272,13 +5253,13 @@
         <v>332</v>
       </c>
       <c r="H47" s="3" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="I47" s="3" t="s">
         <v>334</v>
       </c>
       <c r="J47" s="3" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="K47" s="3">
         <v>10</v>
@@ -5293,13 +5274,13 @@
         <v>150</v>
       </c>
       <c r="O47" s="1" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="P47" s="1" t="s">
-        <v>539</v>
+        <v>537</v>
       </c>
       <c r="Q47" s="4" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="R47" s="3"/>
       <c r="S47" s="3"/>
@@ -5307,7 +5288,7 @@
         <v>1</v>
       </c>
       <c r="AI47" s="1" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="AJ47" s="3">
         <v>150</v>
@@ -5340,10 +5321,10 @@
         <v>373</v>
       </c>
       <c r="H48" s="3" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="I48" s="3" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="J48" s="3" t="s">
         <v>136</v>
@@ -5361,13 +5342,13 @@
         <v>288.3</v>
       </c>
       <c r="O48" s="1" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="P48" s="1" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="Q48" s="4" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="R48" s="3">
         <v>13.4</v>
@@ -5401,7 +5382,7 @@
         <v>26.04</v>
       </c>
       <c r="AR48" s="3" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="AS48" s="3" t="s">
         <v>137</v>
@@ -5427,10 +5408,10 @@
         <v>373</v>
       </c>
       <c r="H49" s="3" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="I49" s="3" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="J49" s="3" t="s">
         <v>138</v>
@@ -5448,13 +5429,13 @@
         <v>119.95</v>
       </c>
       <c r="O49" s="1" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="P49" s="1" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="Q49" s="4" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="R49" s="3">
         <v>14.7</v>
@@ -5514,10 +5495,10 @@
         <v>373</v>
       </c>
       <c r="H50" s="3" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="I50" s="3" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="J50" s="3" t="s">
         <v>142</v>
@@ -5535,11 +5516,11 @@
         <v>16.05</v>
       </c>
       <c r="O50" s="1" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="P50" s="1"/>
       <c r="Q50" s="4" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="R50" s="3"/>
       <c r="S50" s="3"/>
@@ -5562,7 +5543,7 @@
         <v>40</v>
       </c>
       <c r="AI50" s="1" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="AL50" s="3">
         <v>22.1</v>
@@ -5603,10 +5584,10 @@
         <v>373</v>
       </c>
       <c r="H51" s="3" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="I51" s="3" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="J51" s="3" t="s">
         <v>145</v>
@@ -5624,11 +5605,11 @@
         <v>16.05</v>
       </c>
       <c r="O51" s="1" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="P51" s="1"/>
       <c r="Q51" s="4" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="R51" s="3"/>
       <c r="S51" s="3"/>
@@ -5648,7 +5629,7 @@
         <v>66</v>
       </c>
       <c r="AI51" s="1" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="AL51" s="3">
         <v>22.1</v>
@@ -5690,7 +5671,7 @@
         <v>375</v>
       </c>
       <c r="I52" s="3" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="J52" s="3" t="s">
         <v>147</v>
@@ -5708,11 +5689,11 @@
         <v>19.75</v>
       </c>
       <c r="O52" s="1" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="P52" s="1"/>
       <c r="Q52" s="4" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="R52" s="3"/>
       <c r="S52" s="3"/>
@@ -5731,7 +5712,7 @@
       <c r="AE52" s="3"/>
       <c r="AF52" s="3"/>
       <c r="AI52" s="1" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="AJ52" s="3"/>
       <c r="AK52" s="3"/>
@@ -5778,7 +5759,7 @@
         <v>334</v>
       </c>
       <c r="J53" s="3" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="K53" s="3">
         <v>5.44</v>
@@ -5793,13 +5774,13 @@
         <v>3</v>
       </c>
       <c r="O53" s="1" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="P53" s="1" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="Q53" s="4" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="R53" s="3"/>
       <c r="S53" s="3"/>
@@ -5819,7 +5800,7 @@
         <v>4</v>
       </c>
       <c r="AI53" s="1" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="AJ53" s="3"/>
       <c r="AK53" s="3"/>
@@ -5879,13 +5860,13 @@
         <v>3</v>
       </c>
       <c r="O54" s="1" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="P54" s="1" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="Q54" s="4" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="R54" s="3"/>
       <c r="S54" s="3"/>
@@ -5960,13 +5941,13 @@
         <v>3</v>
       </c>
       <c r="O55" s="1" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="P55" s="1" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="Q55" s="4" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="R55" s="3"/>
       <c r="S55" s="3"/>
@@ -6041,13 +6022,13 @@
         <v>3</v>
       </c>
       <c r="O56" s="1" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="P56" s="1" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="Q56" s="4" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="R56" s="3"/>
       <c r="S56" s="3"/>
@@ -6121,13 +6102,13 @@
         <v>3</v>
       </c>
       <c r="O57" s="1" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="P57" s="1" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="Q57" s="4" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="R57" s="3"/>
       <c r="S57" s="3"/>
@@ -6199,13 +6180,13 @@
         <v>3</v>
       </c>
       <c r="O58" s="1" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="P58" s="1" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="Q58" s="4" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="R58" s="3"/>
       <c r="S58" s="3"/>
@@ -6258,13 +6239,13 @@
         <v>373</v>
       </c>
       <c r="H59" s="3" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="I59" s="3" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="J59" s="3" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="K59" s="3">
         <v>12</v>
@@ -6279,13 +6260,13 @@
         <v>74</v>
       </c>
       <c r="O59" s="1" t="s">
+        <v>467</v>
+      </c>
+      <c r="P59" s="1" t="s">
+        <v>535</v>
+      </c>
+      <c r="Q59" s="4" t="s">
         <v>468</v>
-      </c>
-      <c r="P59" s="1" t="s">
-        <v>537</v>
-      </c>
-      <c r="Q59" s="4" t="s">
-        <v>469</v>
       </c>
       <c r="R59" s="3"/>
       <c r="S59" s="3"/>
@@ -6308,7 +6289,7 @@
         <v>1</v>
       </c>
       <c r="AI59" s="1" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="AJ59" s="3">
         <v>74</v>
@@ -6318,7 +6299,7 @@
         <v>17.8</v>
       </c>
       <c r="AR59" s="3" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="AS59" s="3" t="s">
         <v>154</v>
@@ -6347,10 +6328,10 @@
         <v>373</v>
       </c>
       <c r="H60" s="3" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="I60" s="3" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="J60" s="3" t="s">
         <v>155</v>
@@ -6368,13 +6349,13 @@
         <v>74</v>
       </c>
       <c r="O60" s="1" t="s">
+        <v>467</v>
+      </c>
+      <c r="P60" s="1" t="s">
+        <v>535</v>
+      </c>
+      <c r="Q60" s="4" t="s">
         <v>468</v>
-      </c>
-      <c r="P60" s="1" t="s">
-        <v>537</v>
-      </c>
-      <c r="Q60" s="4" t="s">
-        <v>469</v>
       </c>
       <c r="R60" s="3"/>
       <c r="S60" s="3"/>
@@ -6397,7 +6378,7 @@
         <v>1</v>
       </c>
       <c r="AI60" s="1" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="AJ60" s="3">
         <v>74</v>
@@ -6436,10 +6417,10 @@
         <v>373</v>
       </c>
       <c r="H61" s="3" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="I61" s="3" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="J61" s="3" t="s">
         <v>157</v>
@@ -6457,13 +6438,13 @@
         <v>74</v>
       </c>
       <c r="O61" s="1" t="s">
+        <v>467</v>
+      </c>
+      <c r="P61" s="1" t="s">
+        <v>535</v>
+      </c>
+      <c r="Q61" s="4" t="s">
         <v>468</v>
-      </c>
-      <c r="P61" s="1" t="s">
-        <v>537</v>
-      </c>
-      <c r="Q61" s="4" t="s">
-        <v>469</v>
       </c>
       <c r="R61" s="3"/>
       <c r="S61" s="3"/>
@@ -6486,7 +6467,7 @@
         <v>1</v>
       </c>
       <c r="AI61" s="1" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="AJ61" s="3">
         <v>74</v>
@@ -6525,10 +6506,10 @@
         <v>373</v>
       </c>
       <c r="H62" s="3" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="I62" s="3" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="J62" s="3" t="s">
         <v>159</v>
@@ -6546,13 +6527,13 @@
         <v>74</v>
       </c>
       <c r="O62" s="1" t="s">
+        <v>467</v>
+      </c>
+      <c r="P62" s="1" t="s">
+        <v>535</v>
+      </c>
+      <c r="Q62" s="4" t="s">
         <v>468</v>
-      </c>
-      <c r="P62" s="1" t="s">
-        <v>537</v>
-      </c>
-      <c r="Q62" s="4" t="s">
-        <v>469</v>
       </c>
       <c r="R62" s="3"/>
       <c r="S62" s="3"/>
@@ -6575,7 +6556,7 @@
         <v>1</v>
       </c>
       <c r="AI62" s="1" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="AJ62" s="3">
         <v>74</v>
@@ -6611,10 +6592,10 @@
         <v>373</v>
       </c>
       <c r="H63" s="3" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="I63" s="3" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="J63" s="3" t="s">
         <v>378</v>
@@ -6632,11 +6613,11 @@
         <v>0.28999999999999998</v>
       </c>
       <c r="O63" s="1" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="P63" s="1"/>
       <c r="Q63" s="4" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="R63" s="3"/>
       <c r="S63" s="3"/>
@@ -6659,7 +6640,7 @@
         <v>1</v>
       </c>
       <c r="AI63" s="1" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="AJ63" s="3">
         <v>0.28999999999999998</v>
@@ -6698,10 +6679,10 @@
         <v>373</v>
       </c>
       <c r="H64" s="3" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="I64" s="3" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="J64" s="3" t="s">
         <v>353</v>
@@ -6719,11 +6700,11 @@
         <v>0.91</v>
       </c>
       <c r="O64" s="1" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="P64" s="1"/>
       <c r="Q64" s="4" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="R64" s="3"/>
       <c r="S64" s="3"/>
@@ -6746,7 +6727,7 @@
         <v>1</v>
       </c>
       <c r="AI64" s="1" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="AJ64" s="3">
         <v>0.91</v>
@@ -6783,10 +6764,10 @@
         <v>373</v>
       </c>
       <c r="H65" s="3" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="I65" s="3" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="J65" s="3" t="s">
         <v>354</v>
@@ -6804,11 +6785,11 @@
         <v>1.68</v>
       </c>
       <c r="O65" s="1" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="P65" s="1"/>
       <c r="Q65" s="4" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="R65" s="3"/>
       <c r="S65" s="3"/>
@@ -6831,7 +6812,7 @@
         <v>1</v>
       </c>
       <c r="AI65" s="1" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="AJ65" s="3">
         <v>1.68</v>
@@ -6868,10 +6849,10 @@
         <v>373</v>
       </c>
       <c r="H66" s="3" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="I66" s="3" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="J66" s="3" t="s">
         <v>355</v>
@@ -6889,11 +6870,11 @@
         <v>4.12</v>
       </c>
       <c r="O66" s="1" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="P66" s="1"/>
       <c r="Q66" s="4" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="R66" s="3"/>
       <c r="S66" s="3"/>
@@ -6916,7 +6897,7 @@
         <v>1</v>
       </c>
       <c r="AI66" s="1" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="AJ66" s="3">
         <v>4.12</v>
@@ -6953,10 +6934,10 @@
         <v>373</v>
       </c>
       <c r="H67" s="3" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="I67" s="3" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="J67" s="3" t="s">
         <v>356</v>
@@ -6974,11 +6955,11 @@
         <v>0.28999999999999998</v>
       </c>
       <c r="O67" s="1" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="P67" s="1"/>
       <c r="Q67" s="4" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="R67" s="3"/>
       <c r="S67" s="3"/>
@@ -7001,7 +6982,7 @@
         <v>1</v>
       </c>
       <c r="AI67" s="1" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="AJ67" s="3">
         <v>0.28999999999999998</v>
@@ -7038,10 +7019,10 @@
         <v>373</v>
       </c>
       <c r="H68" s="3" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="I68" s="3" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="J68" s="3" t="s">
         <v>357</v>
@@ -7059,11 +7040,11 @@
         <v>0.91</v>
       </c>
       <c r="O68" s="1" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="P68" s="1"/>
       <c r="Q68" s="4" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="R68" s="3"/>
       <c r="S68" s="3"/>
@@ -7086,7 +7067,7 @@
         <v>1</v>
       </c>
       <c r="AI68" s="1" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="AJ68" s="3">
         <v>0.91</v>
@@ -7123,10 +7104,10 @@
         <v>373</v>
       </c>
       <c r="H69" s="3" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="I69" s="3" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="J69" s="3" t="s">
         <v>358</v>
@@ -7144,11 +7125,11 @@
         <v>1.68</v>
       </c>
       <c r="O69" s="1" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="P69" s="1"/>
       <c r="Q69" s="4" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="R69" s="3"/>
       <c r="S69" s="3"/>
@@ -7171,7 +7152,7 @@
         <v>1</v>
       </c>
       <c r="AI69" s="1" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="AJ69" s="3">
         <v>1.68</v>
@@ -7208,10 +7189,10 @@
         <v>373</v>
       </c>
       <c r="H70" s="3" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="I70" s="3" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="J70" s="3" t="s">
         <v>359</v>
@@ -7229,11 +7210,11 @@
         <v>4.12</v>
       </c>
       <c r="O70" s="1" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="P70" s="1"/>
       <c r="Q70" s="4" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="R70" s="3"/>
       <c r="S70" s="3"/>
@@ -7256,7 +7237,7 @@
         <v>1</v>
       </c>
       <c r="AI70" s="1" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="AJ70" s="3">
         <v>4.12</v>
@@ -7293,10 +7274,10 @@
         <v>373</v>
       </c>
       <c r="H71" s="3" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="I71" s="3" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="J71" s="3" t="s">
         <v>360</v>
@@ -7314,11 +7295,11 @@
         <v>0.28999999999999998</v>
       </c>
       <c r="O71" s="1" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="P71" s="1"/>
       <c r="Q71" s="4" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="R71" s="3"/>
       <c r="S71" s="3"/>
@@ -7341,7 +7322,7 @@
         <v>1</v>
       </c>
       <c r="AI71" s="1" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="AJ71" s="3">
         <v>0.28999999999999998</v>
@@ -7377,10 +7358,10 @@
         <v>373</v>
       </c>
       <c r="H72" s="3" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="I72" s="3" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="J72" s="3" t="s">
         <v>361</v>
@@ -7398,11 +7379,11 @@
         <v>0.91</v>
       </c>
       <c r="O72" s="1" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="P72" s="1"/>
       <c r="Q72" s="4" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="R72" s="3"/>
       <c r="S72" s="3"/>
@@ -7425,7 +7406,7 @@
         <v>1</v>
       </c>
       <c r="AI72" s="1" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="AJ72" s="3">
         <v>0.91</v>
@@ -7461,10 +7442,10 @@
         <v>373</v>
       </c>
       <c r="H73" s="3" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="I73" s="3" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="J73" s="3" t="s">
         <v>362</v>
@@ -7482,11 +7463,11 @@
         <v>1.68</v>
       </c>
       <c r="O73" s="1" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="P73" s="1"/>
       <c r="Q73" s="4" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="R73" s="3"/>
       <c r="S73" s="3"/>
@@ -7509,7 +7490,7 @@
         <v>1</v>
       </c>
       <c r="AI73" s="1" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="AJ73" s="3">
         <v>1.68</v>
@@ -7545,10 +7526,10 @@
         <v>373</v>
       </c>
       <c r="H74" s="3" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="I74" s="3" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="J74" s="3" t="s">
         <v>363</v>
@@ -7566,11 +7547,11 @@
         <v>4.12</v>
       </c>
       <c r="O74" s="1" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="P74" s="1"/>
       <c r="Q74" s="4" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="R74" s="3"/>
       <c r="S74" s="3"/>
@@ -7593,7 +7574,7 @@
         <v>1</v>
       </c>
       <c r="AI74" s="1" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="AJ74" s="3">
         <v>4.12</v>
@@ -7629,10 +7610,10 @@
         <v>373</v>
       </c>
       <c r="H75" s="3" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="I75" s="3" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="J75" s="3" t="s">
         <v>364</v>
@@ -7650,11 +7631,11 @@
         <v>0.28999999999999998</v>
       </c>
       <c r="O75" s="1" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="P75" s="1"/>
       <c r="Q75" s="4" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="R75" s="3"/>
       <c r="S75" s="3"/>
@@ -7677,7 +7658,7 @@
         <v>1</v>
       </c>
       <c r="AI75" s="1" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="AJ75" s="3">
         <v>0.28999999999999998</v>
@@ -7713,10 +7694,10 @@
         <v>373</v>
       </c>
       <c r="H76" s="3" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="I76" s="3" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="J76" s="3" t="s">
         <v>365</v>
@@ -7734,11 +7715,11 @@
         <v>0.91</v>
       </c>
       <c r="O76" s="1" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="P76" s="1"/>
       <c r="Q76" s="4" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="R76" s="3"/>
       <c r="S76" s="3"/>
@@ -7761,7 +7742,7 @@
         <v>1</v>
       </c>
       <c r="AI76" s="1" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="AJ76" s="3">
         <v>0.91</v>
@@ -7797,10 +7778,10 @@
         <v>373</v>
       </c>
       <c r="H77" s="3" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="I77" s="3" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="J77" s="3" t="s">
         <v>366</v>
@@ -7818,11 +7799,11 @@
         <v>1.68</v>
       </c>
       <c r="O77" s="1" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="P77" s="1"/>
       <c r="Q77" s="4" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="R77" s="3"/>
       <c r="S77" s="3"/>
@@ -7845,7 +7826,7 @@
         <v>1</v>
       </c>
       <c r="AI77" s="1" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="AJ77" s="3">
         <v>1.68</v>
@@ -7881,10 +7862,10 @@
         <v>373</v>
       </c>
       <c r="H78" s="3" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="I78" s="3" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="J78" s="3" t="s">
         <v>367</v>
@@ -7902,11 +7883,11 @@
         <v>4.12</v>
       </c>
       <c r="O78" s="1" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="P78" s="1"/>
       <c r="Q78" s="4" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="R78" s="3"/>
       <c r="S78" s="3"/>
@@ -7929,7 +7910,7 @@
         <v>1</v>
       </c>
       <c r="AI78" s="1" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="AJ78" s="3">
         <v>4.12</v>
@@ -7971,7 +7952,7 @@
         <v>335</v>
       </c>
       <c r="J79" s="3" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="K79" s="3">
         <v>12</v>
@@ -7986,11 +7967,11 @@
         <v>3.34</v>
       </c>
       <c r="O79" s="1" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="P79" s="1"/>
       <c r="Q79" s="4" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="R79" s="3"/>
       <c r="S79" s="3"/>
@@ -8004,7 +7985,7 @@
         <v>24</v>
       </c>
       <c r="AI79" s="1" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="AJ79" s="3">
         <v>3.34</v>
@@ -8013,7 +7994,7 @@
         <v>48</v>
       </c>
       <c r="AR79" s="3" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="AS79" s="3" t="s">
         <v>164</v>
@@ -8063,11 +8044,11 @@
         <v>3.34</v>
       </c>
       <c r="O80" s="1" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="P80" s="1"/>
       <c r="Q80" s="4" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="R80" s="3"/>
       <c r="S80" s="3"/>
@@ -8081,7 +8062,7 @@
         <v>24</v>
       </c>
       <c r="AI80" s="1" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="AJ80" s="3">
         <v>3.34</v>
@@ -8140,11 +8121,11 @@
         <v>3.34</v>
       </c>
       <c r="O81" s="1" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="P81" s="1"/>
       <c r="Q81" s="4" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="R81" s="3"/>
       <c r="S81" s="3"/>
@@ -8158,7 +8139,7 @@
         <v>24</v>
       </c>
       <c r="AI81" s="1" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="AJ81" s="3">
         <v>3.34</v>
@@ -8217,11 +8198,11 @@
         <v>3.34</v>
       </c>
       <c r="O82" s="1" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="P82" s="1"/>
       <c r="Q82" s="4" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="R82" s="3"/>
       <c r="S82" s="3"/>
@@ -8235,7 +8216,7 @@
         <v>24</v>
       </c>
       <c r="AI82" s="1" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="AJ82" s="3">
         <v>3.34</v>
@@ -8294,11 +8275,11 @@
         <v>3.34</v>
       </c>
       <c r="O83" s="1" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="P83" s="1"/>
       <c r="Q83" s="4" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="R83" s="3"/>
       <c r="S83" s="3"/>
@@ -8312,7 +8293,7 @@
         <v>24</v>
       </c>
       <c r="AI83" s="1" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="AJ83" s="3">
         <v>3.34</v>
@@ -8371,11 +8352,11 @@
         <v>3.34</v>
       </c>
       <c r="O84" s="1" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="P84" s="1"/>
       <c r="Q84" s="4" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="R84" s="3"/>
       <c r="S84" s="3"/>
@@ -8389,7 +8370,7 @@
         <v>24</v>
       </c>
       <c r="AI84" s="1" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="AJ84" s="3">
         <v>3.34</v>
@@ -8448,11 +8429,11 @@
         <v>3.34</v>
       </c>
       <c r="O85" s="1" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="P85" s="1"/>
       <c r="Q85" s="4" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="R85" s="3"/>
       <c r="S85" s="3"/>
@@ -8466,7 +8447,7 @@
         <v>24</v>
       </c>
       <c r="AI85" s="1" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="AJ85" s="3">
         <v>3.34</v>
@@ -8525,11 +8506,11 @@
         <v>3.34</v>
       </c>
       <c r="O86" s="1" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="P86" s="1"/>
       <c r="Q86" s="4" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="R86" s="3"/>
       <c r="S86" s="3"/>
@@ -8543,7 +8524,7 @@
         <v>24</v>
       </c>
       <c r="AI86" s="1" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="AJ86" s="3">
         <v>3.34</v>
@@ -8587,7 +8568,7 @@
         <v>334</v>
       </c>
       <c r="J87" s="3" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="K87" s="3">
         <v>10.5</v>
@@ -8602,13 +8583,13 @@
         <v>1179</v>
       </c>
       <c r="O87" s="1" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="P87" s="1" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="Q87" s="4" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="R87" s="3"/>
       <c r="S87" s="3"/>
@@ -8622,13 +8603,13 @@
         <v>1</v>
       </c>
       <c r="AI87" s="1" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="AQ87" s="3">
         <v>48</v>
       </c>
       <c r="AR87" s="3" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="AS87" s="3" t="s">
         <v>173</v>
@@ -8651,10 +8632,10 @@
         <v>123</v>
       </c>
       <c r="G88" s="3" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="H88" s="3" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="I88" s="3" t="s">
         <v>379</v>
@@ -8675,13 +8656,13 @@
         <v>580</v>
       </c>
       <c r="O88" s="1" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="P88" s="1" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="Q88" s="4" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="R88" s="3"/>
       <c r="S88" s="3"/>
@@ -8740,7 +8721,7 @@
         <v>79</v>
       </c>
       <c r="Q89" s="4" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="R89" s="3">
         <v>1.7</v>
@@ -8759,7 +8740,7 @@
       </c>
       <c r="X89" s="3"/>
       <c r="AR89" s="3" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="AS89" s="3" t="s">
         <v>176</v>
@@ -8809,13 +8790,13 @@
         <v>0.33900000000000002</v>
       </c>
       <c r="O90" s="1" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="P90" s="1" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="Q90" s="4" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="R90" s="3"/>
       <c r="S90" s="3"/>
@@ -8882,13 +8863,13 @@
         <v>0.33900000000000002</v>
       </c>
       <c r="O91" s="1" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="P91" s="1" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="Q91" s="4" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="R91" s="3"/>
       <c r="S91" s="3"/>
@@ -8955,13 +8936,13 @@
         <v>0.33900000000000002</v>
       </c>
       <c r="O92" s="1" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="P92" s="1" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="Q92" s="4" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="R92" s="3"/>
       <c r="S92" s="3"/>
@@ -9010,10 +8991,10 @@
         <v>373</v>
       </c>
       <c r="H93" s="3" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="I93" s="3" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="J93" s="3" t="s">
         <v>385</v>
@@ -9031,13 +9012,13 @@
         <v>1.37</v>
       </c>
       <c r="O93" s="1" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="P93" s="3" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="Q93" s="4" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="T93" s="3">
         <v>0.06</v>
@@ -9083,10 +9064,10 @@
         <v>373</v>
       </c>
       <c r="H94" s="3" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="I94" s="3" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="K94" s="3">
         <v>16</v>
@@ -9101,13 +9082,13 @@
         <v>0.33</v>
       </c>
       <c r="O94" s="1" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="P94" s="3" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="Q94" s="4" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="U94" s="1" t="s">
         <v>223</v>
@@ -9150,13 +9131,13 @@
         <v>332</v>
       </c>
       <c r="H95" s="3" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="I95" s="3" t="s">
         <v>335</v>
       </c>
       <c r="J95" s="3" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="K95" s="3">
         <v>10</v>
@@ -9171,13 +9152,13 @@
         <v>2.3E-3</v>
       </c>
       <c r="O95" s="1" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="P95" s="1" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
       <c r="Q95" s="4" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="R95" s="3"/>
       <c r="S95" s="3"/>
@@ -9190,7 +9171,7 @@
         <v>1</v>
       </c>
       <c r="AI95" s="1" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="AJ95" s="3">
         <v>2.3E-3</v>
@@ -9226,7 +9207,7 @@
         <v>332</v>
       </c>
       <c r="H96" s="3" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="I96" s="3" t="s">
         <v>335</v>
@@ -9247,13 +9228,13 @@
         <v>1.55E-2</v>
       </c>
       <c r="O96" s="1" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="P96" s="1" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="Q96" s="4" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="R96" s="3"/>
       <c r="S96" s="3"/>
@@ -9266,7 +9247,7 @@
         <v>1</v>
       </c>
       <c r="AI96" s="1" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="AJ96" s="3">
         <v>1.55E-2</v>
@@ -9299,13 +9280,13 @@
         <v>373</v>
       </c>
       <c r="H97" s="3" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="I97" s="3" t="s">
-        <v>493</v>
-      </c>
-      <c r="J97" s="3" t="s">
-        <v>387</v>
+        <v>492</v>
+      </c>
+      <c r="J97" s="7" t="s">
+        <v>544</v>
       </c>
       <c r="K97" s="3">
         <v>17</v>
@@ -9320,11 +9301,11 @@
         <v>109.98</v>
       </c>
       <c r="O97" s="1" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="P97" s="1"/>
       <c r="Q97" s="6" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="U97" s="1" t="s">
         <v>223</v>
@@ -9336,7 +9317,7 @@
         <v>7</v>
       </c>
       <c r="AI97" s="1" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="AJ97">
         <v>109.98</v>
@@ -9374,7 +9355,7 @@
         <v>335</v>
       </c>
       <c r="J98" s="3" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="K98" s="3">
         <v>9</v>
@@ -9389,20 +9370,20 @@
         <v>17.3</v>
       </c>
       <c r="O98" s="1" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="P98" s="1"/>
       <c r="Q98" s="4" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="AI98" s="1" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="AJ98">
         <v>17.3</v>
       </c>
       <c r="AR98" s="1" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="AS98" s="3" t="s">
         <v>242</v>
@@ -9435,7 +9416,7 @@
         <v>379</v>
       </c>
       <c r="J99" s="7" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="K99">
         <v>8.1</v>
@@ -9447,13 +9428,13 @@
         <v>79</v>
       </c>
       <c r="O99" s="1" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="P99" s="1" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="Q99" s="4" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="U99" s="1" t="s">
         <v>223</v>
@@ -9505,13 +9486,13 @@
         <v>79</v>
       </c>
       <c r="O100" s="1" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="P100" s="1" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="Q100" s="4" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="U100" s="1" t="s">
         <v>223</v>
@@ -9543,13 +9524,13 @@
         <v>22</v>
       </c>
       <c r="G101" s="3" t="s">
+        <v>392</v>
+      </c>
+      <c r="H101" s="3" t="s">
         <v>393</v>
       </c>
-      <c r="H101" s="3" t="s">
-        <v>394</v>
-      </c>
       <c r="I101" s="3" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="J101" s="3" t="s">
         <v>249</v>
@@ -9567,13 +9548,13 @@
         <v>185</v>
       </c>
       <c r="O101" s="1" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="P101" s="1" t="s">
-        <v>539</v>
+        <v>537</v>
       </c>
       <c r="Q101" s="4" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="U101" s="1" t="s">
         <v>223</v>
@@ -9582,7 +9563,7 @@
         <v>200</v>
       </c>
       <c r="AR101" s="8" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="AS101" s="3" t="s">
         <v>250</v>
@@ -9608,10 +9589,10 @@
         <v>332</v>
       </c>
       <c r="H102" s="3" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="I102" s="3" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="J102" t="s">
         <v>243</v>
@@ -9627,13 +9608,13 @@
       </c>
       <c r="P102" s="1"/>
       <c r="Q102" s="4" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="AN102">
         <v>8.65</v>
       </c>
       <c r="AR102" s="1" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="AS102" s="3" t="s">
         <v>244</v>
@@ -9665,7 +9646,7 @@
         <v>334</v>
       </c>
       <c r="J103" s="3" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="K103">
         <v>10</v>
@@ -9680,13 +9661,13 @@
         <v>601</v>
       </c>
       <c r="O103" s="1" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="P103" s="1" t="s">
-        <v>539</v>
+        <v>537</v>
       </c>
       <c r="Q103" s="4" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="T103">
         <v>2.6</v>
@@ -9742,13 +9723,13 @@
         <v>561</v>
       </c>
       <c r="O104" s="1" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="P104" s="1" t="s">
-        <v>539</v>
+        <v>537</v>
       </c>
       <c r="Q104" s="4" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="T104">
         <v>3.7</v>
@@ -9801,13 +9782,13 @@
         <v>542</v>
       </c>
       <c r="O105" s="1" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="P105" s="1" t="s">
-        <v>539</v>
+        <v>537</v>
       </c>
       <c r="Q105" s="4" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="T105">
         <v>2.9</v>
@@ -9845,13 +9826,13 @@
         <v>332</v>
       </c>
       <c r="H106" s="3" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="I106" s="3" t="s">
         <v>335</v>
       </c>
       <c r="J106" s="7" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="K106">
         <v>12.5</v>
@@ -9866,11 +9847,11 @@
         <v>120</v>
       </c>
       <c r="O106" s="1" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="P106" s="1"/>
       <c r="Q106" s="4" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="T106">
         <v>0.5</v>
@@ -9891,13 +9872,13 @@
         <v>7</v>
       </c>
       <c r="AI106" s="1" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="AP106" s="1" t="s">
         <v>262</v>
       </c>
       <c r="AR106" s="1" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="AS106" s="3" t="s">
         <v>263</v>
@@ -9926,7 +9907,7 @@
         <v>332</v>
       </c>
       <c r="H107" s="3" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="I107" s="3" t="s">
         <v>335</v>
@@ -9947,11 +9928,11 @@
         <v>120</v>
       </c>
       <c r="O107" s="1" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="P107" s="1"/>
       <c r="Q107" s="4" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="T107">
         <v>0.4</v>
@@ -9972,7 +9953,7 @@
         <v>7</v>
       </c>
       <c r="AI107" s="1" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="AP107" s="1" t="s">
         <v>262</v>
@@ -10004,7 +9985,7 @@
         <v>332</v>
       </c>
       <c r="H108" s="3" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="I108" s="3" t="s">
         <v>335</v>
@@ -10025,11 +10006,11 @@
         <v>120</v>
       </c>
       <c r="O108" s="1" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="P108" s="1"/>
       <c r="Q108" s="4" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="T108">
         <v>0.5</v>
@@ -10050,7 +10031,7 @@
         <v>7</v>
       </c>
       <c r="AI108" s="1" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="AP108" s="1" t="s">
         <v>262</v>
@@ -10085,7 +10066,7 @@
         <v>335</v>
       </c>
       <c r="J109" s="1" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="K109">
         <v>8</v>
@@ -10104,7 +10085,7 @@
       </c>
       <c r="P109" s="1"/>
       <c r="Q109" s="4" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="U109" s="1" t="s">
         <v>220</v>
@@ -10116,7 +10097,7 @@
         <v>560.5</v>
       </c>
       <c r="AR109" s="1" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="AS109" s="3" t="s">
         <v>268</v>
@@ -10145,7 +10126,7 @@
         <v>335</v>
       </c>
       <c r="J110" s="3" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="K110">
         <v>4</v>
@@ -10164,7 +10145,7 @@
       </c>
       <c r="P110" s="1"/>
       <c r="Q110" s="4" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="U110" s="1" t="s">
         <v>220</v>
@@ -10203,7 +10184,7 @@
         <v>335</v>
       </c>
       <c r="J111" s="3" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="K111">
         <v>8</v>
@@ -10218,17 +10199,17 @@
         <v>483</v>
       </c>
       <c r="O111" s="1" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="P111" s="1"/>
       <c r="Q111" s="4" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="U111" s="1" t="s">
         <v>220</v>
       </c>
       <c r="AI111" s="1" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="AJ111">
         <v>483</v>
@@ -10261,7 +10242,7 @@
         <v>335</v>
       </c>
       <c r="J112" s="3" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="K112">
         <v>14</v>
@@ -10276,17 +10257,17 @@
         <v>569</v>
       </c>
       <c r="O112" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="P112" s="1"/>
       <c r="Q112" s="4" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="U112" s="1" t="s">
         <v>220</v>
       </c>
       <c r="AI112" s="1" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="AJ112">
         <v>569</v>
@@ -10319,7 +10300,7 @@
         <v>335</v>
       </c>
       <c r="J113" s="3" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="K113">
         <v>14</v>
@@ -10334,17 +10315,17 @@
         <v>488</v>
       </c>
       <c r="O113" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="P113" s="1"/>
       <c r="Q113" s="4" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="U113" s="1" t="s">
         <v>220</v>
       </c>
       <c r="AI113" s="1" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="AJ113">
         <v>488</v>
@@ -10377,7 +10358,7 @@
         <v>335</v>
       </c>
       <c r="J114" s="3" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="K114">
         <v>14</v>
@@ -10392,17 +10373,17 @@
         <v>522</v>
       </c>
       <c r="O114" s="1" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="P114" s="1"/>
       <c r="Q114" s="4" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="U114" s="1" t="s">
         <v>220</v>
       </c>
       <c r="AI114" s="1" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="AJ114">
         <v>522</v>
@@ -10432,13 +10413,13 @@
         <v>332</v>
       </c>
       <c r="H115" s="3" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="I115" s="3" t="s">
         <v>335</v>
       </c>
       <c r="J115" s="3" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="K115">
         <v>10</v>
@@ -10453,7 +10434,7 @@
         <v>350</v>
       </c>
       <c r="Q115" s="4" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="U115" s="1" t="s">
         <v>220</v>
@@ -10501,13 +10482,13 @@
         <v>332</v>
       </c>
       <c r="H116" s="3" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="I116" s="3" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="J116" s="3" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="K116">
         <v>12</v>
@@ -10522,7 +10503,7 @@
         <v>622.1</v>
       </c>
       <c r="Q116" s="4" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="U116" s="1" t="s">
         <v>220</v>
@@ -10575,13 +10556,13 @@
         <v>11</v>
       </c>
       <c r="G117" s="3" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="H117" s="3" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="I117" s="3" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="J117" s="3" t="s">
         <v>279</v>
@@ -10599,7 +10580,7 @@
         <v>700</v>
       </c>
       <c r="Q117" s="4" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="U117" s="1" t="s">
         <v>220</v>
@@ -10661,16 +10642,16 @@
         <v>286</v>
       </c>
       <c r="G118" s="3" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="H118" s="3" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="I118" s="3" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="J118" s="3" t="s">
-        <v>515</v>
+        <v>545</v>
       </c>
       <c r="K118">
         <v>14.9</v>
@@ -10682,11 +10663,11 @@
         <v>5</v>
       </c>
       <c r="O118" s="1" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="P118" s="1"/>
       <c r="Q118" s="4" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="AA118">
         <v>33.299999999999997</v>
@@ -10695,7 +10676,7 @@
         <v>6</v>
       </c>
       <c r="AI118" s="1" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="AR118" s="1" t="s">
         <v>283</v>
@@ -10724,13 +10705,13 @@
         <v>286</v>
       </c>
       <c r="G119" s="3" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="H119" s="3" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="I119" s="3" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="J119" s="3" t="s">
         <v>284</v>
@@ -10745,11 +10726,11 @@
         <v>5</v>
       </c>
       <c r="O119" s="1" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="P119" s="1"/>
       <c r="Q119" s="4" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="AA119">
         <v>33.299999999999997</v>
@@ -10758,7 +10739,7 @@
         <v>6</v>
       </c>
       <c r="AI119" s="1" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="AS119" s="3" t="s">
         <v>288</v>
@@ -10784,13 +10765,13 @@
         <v>286</v>
       </c>
       <c r="G120" s="3" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="H120" s="3" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="I120" s="3" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="J120" s="3" t="s">
         <v>285</v>
@@ -10805,11 +10786,11 @@
         <v>5</v>
       </c>
       <c r="O120" s="1" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="P120" s="1"/>
       <c r="Q120" s="4" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="AA120">
         <v>33.299999999999997</v>
@@ -10818,7 +10799,7 @@
         <v>6</v>
       </c>
       <c r="AI120" s="1" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="AR120" s="1" t="s">
         <v>290</v>
@@ -10850,10 +10831,10 @@
         <v>373</v>
       </c>
       <c r="H121" s="3" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="I121" s="3" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="J121" s="3" t="s">
         <v>299</v>
@@ -10872,7 +10853,7 @@
       </c>
       <c r="P121" s="1"/>
       <c r="Q121" s="4" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="T121">
         <v>0.04</v>
@@ -10910,10 +10891,10 @@
         <v>373</v>
       </c>
       <c r="H122" s="3" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="I122" s="3" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="J122" s="3" t="s">
         <v>299</v>
@@ -10932,7 +10913,7 @@
       </c>
       <c r="P122" s="1"/>
       <c r="Q122" s="4" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="T122">
         <v>0.04</v>
@@ -10970,10 +10951,10 @@
         <v>373</v>
       </c>
       <c r="H123" s="3" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="I123" s="3" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="J123" s="3" t="s">
         <v>299</v>
@@ -10992,7 +10973,7 @@
       </c>
       <c r="P123" s="1"/>
       <c r="Q123" s="4" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="T123">
         <v>0.05</v>
@@ -11030,10 +11011,10 @@
         <v>373</v>
       </c>
       <c r="H124" s="3" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="I124" s="3" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="J124" s="3" t="s">
         <v>299</v>
@@ -11052,7 +11033,7 @@
       </c>
       <c r="P124" s="1"/>
       <c r="Q124" s="4" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="T124">
         <v>7.0000000000000007E-2</v>
@@ -11090,10 +11071,10 @@
         <v>373</v>
       </c>
       <c r="H125" s="3" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="I125" s="3" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="J125" s="3" t="s">
         <v>299</v>
@@ -11112,7 +11093,7 @@
       </c>
       <c r="P125" s="1"/>
       <c r="Q125" s="4" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="T125">
         <v>0.6</v>
@@ -11150,10 +11131,10 @@
         <v>373</v>
       </c>
       <c r="H126" s="3" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="I126" s="3" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="J126" s="3" t="s">
         <v>299</v>
@@ -11172,7 +11153,7 @@
       </c>
       <c r="P126" s="1"/>
       <c r="Q126" s="4" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="T126">
         <v>0.01</v>
@@ -11210,10 +11191,10 @@
         <v>373</v>
       </c>
       <c r="H127" s="3" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="I127" s="3" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="J127" s="3" t="s">
         <v>299</v>
@@ -11232,7 +11213,7 @@
       </c>
       <c r="P127" s="1"/>
       <c r="Q127" s="4" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="T127">
         <v>0.05</v>
@@ -11270,10 +11251,10 @@
         <v>373</v>
       </c>
       <c r="H128" s="3" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="I128" s="3" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="J128" s="3" t="s">
         <v>299</v>
@@ -11292,7 +11273,7 @@
       </c>
       <c r="P128" s="1"/>
       <c r="Q128" s="4" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="T128">
         <v>0.06</v>
@@ -11330,10 +11311,10 @@
         <v>373</v>
       </c>
       <c r="H129" s="3" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="I129" s="3" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="J129" s="3" t="s">
         <v>299</v>
@@ -11352,7 +11333,7 @@
       </c>
       <c r="P129" s="1"/>
       <c r="Q129" s="4" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="T129">
         <v>0.08</v>
@@ -11390,10 +11371,10 @@
         <v>373</v>
       </c>
       <c r="H130" s="3" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="I130" s="3" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="J130" s="3" t="s">
         <v>299</v>
@@ -11412,7 +11393,7 @@
       </c>
       <c r="P130" s="1"/>
       <c r="Q130" s="4" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="U130" s="1" t="s">
         <v>220</v>
@@ -11447,10 +11428,10 @@
         <v>373</v>
       </c>
       <c r="H131" s="3" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="I131" s="3" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="J131" s="3" t="s">
         <v>299</v>
@@ -11469,7 +11450,7 @@
       </c>
       <c r="P131" s="1"/>
       <c r="Q131" s="4" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="T131">
         <v>0.04</v>
@@ -11507,10 +11488,10 @@
         <v>373</v>
       </c>
       <c r="H132" s="3" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="I132" s="3" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="J132" s="3" t="s">
         <v>299</v>
@@ -11529,7 +11510,7 @@
       </c>
       <c r="P132" s="1"/>
       <c r="Q132" s="4" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="T132">
         <v>0.03</v>
@@ -11567,10 +11548,10 @@
         <v>373</v>
       </c>
       <c r="H133" s="3" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="I133" s="3" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="J133" s="3" t="s">
         <v>299</v>
@@ -11589,7 +11570,7 @@
       </c>
       <c r="P133" s="1"/>
       <c r="Q133" s="4" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="T133">
         <v>0.04</v>
@@ -11627,10 +11608,10 @@
         <v>373</v>
       </c>
       <c r="H134" s="3" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="I134" s="3" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="J134" s="3" t="s">
         <v>299</v>
@@ -11649,7 +11630,7 @@
       </c>
       <c r="P134" s="1"/>
       <c r="Q134" s="4" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="T134">
         <v>0.14000000000000001</v>
@@ -11687,10 +11668,10 @@
         <v>373</v>
       </c>
       <c r="H135" s="3" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="I135" s="3" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="J135" s="3" t="s">
         <v>299</v>
@@ -11709,7 +11690,7 @@
       </c>
       <c r="P135" s="1"/>
       <c r="Q135" s="4" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="U135" s="1" t="s">
         <v>220</v>
@@ -11744,10 +11725,10 @@
         <v>373</v>
       </c>
       <c r="H136" s="3" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="I136" s="3" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="J136" s="3" t="s">
         <v>299</v>
@@ -11766,7 +11747,7 @@
       </c>
       <c r="P136" s="1"/>
       <c r="Q136" s="4" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="T136">
         <v>7.0000000000000007E-2</v>
@@ -11804,10 +11785,10 @@
         <v>373</v>
       </c>
       <c r="H137" s="3" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="I137" s="3" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="J137" s="3" t="s">
         <v>299</v>
@@ -11826,7 +11807,7 @@
       </c>
       <c r="P137" s="1"/>
       <c r="Q137" s="4" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="T137">
         <v>0.01</v>
@@ -11864,10 +11845,10 @@
         <v>373</v>
       </c>
       <c r="H138" s="3" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="I138" s="3" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="J138" s="3" t="s">
         <v>299</v>
@@ -11886,7 +11867,7 @@
       </c>
       <c r="P138" s="1"/>
       <c r="Q138" s="4" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="T138">
         <v>0.05</v>
@@ -11924,10 +11905,10 @@
         <v>373</v>
       </c>
       <c r="H139" s="3" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="I139" s="3" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="J139" s="3" t="s">
         <v>299</v>
@@ -11946,7 +11927,7 @@
       </c>
       <c r="P139" s="1"/>
       <c r="Q139" s="4" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="T139">
         <v>0.03</v>
@@ -11984,10 +11965,10 @@
         <v>373</v>
       </c>
       <c r="H140" s="3" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="I140" s="3" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="J140" s="3" t="s">
         <v>299</v>
@@ -12006,7 +11987,7 @@
       </c>
       <c r="P140" s="1"/>
       <c r="Q140" s="4" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="U140" s="1" t="s">
         <v>220</v>
@@ -12041,10 +12022,10 @@
         <v>373</v>
       </c>
       <c r="H141" s="3" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="I141" s="3" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="J141" s="3" t="s">
         <v>299</v>
@@ -12063,7 +12044,7 @@
       </c>
       <c r="P141" s="1"/>
       <c r="Q141" s="4" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="U141" s="1" t="s">
         <v>220</v>
@@ -12098,10 +12079,10 @@
         <v>373</v>
       </c>
       <c r="H142" s="3" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="I142" s="3" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="J142" s="3" t="s">
         <v>299</v>
@@ -12120,7 +12101,7 @@
       </c>
       <c r="P142" s="1"/>
       <c r="Q142" s="4" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="U142" s="1" t="s">
         <v>220</v>
@@ -12155,10 +12136,10 @@
         <v>373</v>
       </c>
       <c r="H143" s="3" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="I143" s="3" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="J143" s="3" t="s">
         <v>299</v>
@@ -12177,7 +12158,7 @@
       </c>
       <c r="P143" s="1"/>
       <c r="Q143" s="4" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="T143">
         <v>7.0000000000000007E-2</v>
@@ -12215,10 +12196,10 @@
         <v>373</v>
       </c>
       <c r="H144" s="3" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="I144" s="3" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="J144" s="3" t="s">
         <v>299</v>
@@ -12237,7 +12218,7 @@
       </c>
       <c r="P144" s="1"/>
       <c r="Q144" s="4" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="T144">
         <v>0.1</v>
@@ -12275,10 +12256,10 @@
         <v>373</v>
       </c>
       <c r="H145" s="3" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="I145" s="3" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="J145" s="3" t="s">
         <v>299</v>
@@ -12297,7 +12278,7 @@
       </c>
       <c r="P145" s="1"/>
       <c r="Q145" s="4" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="T145">
         <v>7.0000000000000007E-2</v>
@@ -12335,10 +12316,10 @@
         <v>373</v>
       </c>
       <c r="H146" s="3" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="I146" s="3" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="J146" s="3" t="s">
         <v>299</v>
@@ -12357,7 +12338,7 @@
       </c>
       <c r="P146" s="1"/>
       <c r="Q146" s="4" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="T146">
         <v>0.05</v>
@@ -12395,10 +12376,10 @@
         <v>373</v>
       </c>
       <c r="H147" s="3" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="I147" s="3" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="J147" s="3" t="s">
         <v>299</v>
@@ -12417,7 +12398,7 @@
       </c>
       <c r="P147" s="1"/>
       <c r="Q147" s="4" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="T147">
         <v>0.13</v>
@@ -12455,10 +12436,10 @@
         <v>373</v>
       </c>
       <c r="H148" s="3" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="I148" s="3" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="J148" s="3" t="s">
         <v>299</v>
@@ -12477,7 +12458,7 @@
       </c>
       <c r="P148" s="1"/>
       <c r="Q148" s="4" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="T148">
         <v>0.1</v>
@@ -12515,10 +12496,10 @@
         <v>373</v>
       </c>
       <c r="H149" s="3" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="I149" s="3" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="J149" s="3" t="s">
         <v>299</v>
@@ -12537,7 +12518,7 @@
       </c>
       <c r="P149" s="1"/>
       <c r="Q149" s="4" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="T149">
         <v>7.0000000000000007E-2</v>
@@ -12575,10 +12556,10 @@
         <v>373</v>
       </c>
       <c r="H150" s="3" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="I150" s="3" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="J150" s="3" t="s">
         <v>299</v>
@@ -12597,7 +12578,7 @@
       </c>
       <c r="P150" s="1"/>
       <c r="Q150" s="4" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="U150" s="1" t="s">
         <v>220</v>
